--- a/public/templates/examples/A-005-RACIMatrixforCybersecurity-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-005-RACIMatrixforCybersecurity-EXAMPLE-L.xlsx
@@ -1474,7 +1474,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>RACI Matrix — How to use</t>
+          <t>RACI Matrix: How to use</t>
         </is>
       </c>
     </row>

--- a/public/templates/examples/A-005-RACIMatrixforCybersecurity-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-005-RACIMatrixforCybersecurity-EXAMPLE-L.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -220,12 +220,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="533400" cy="533400"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -389,7 +389,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -423,7 +423,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
